--- a/input/03_input_bapp_ppl_t2.xlsx
+++ b/input/03_input_bapp_ppl_t2.xlsx
@@ -54,7 +54,7 @@
     <t>001</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1u87uDsnJTOAOBEGdiFob_NB_8ze9H8pw</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>6304XXXXXXXX</t>
